--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -13749,7 +13749,7 @@
         <v>4.628886712605407</v>
       </c>
       <c r="F483" t="n">
-        <v>4.879767018891217</v>
+        <v>4.880526608749236</v>
       </c>
       <c r="G483" t="n">
         <v>4.696837374513915</v>
@@ -13844,7 +13844,7 @@
         <v>4.622027303054514</v>
       </c>
       <c r="F486" t="n">
-        <v>4.843399374720342</v>
+        <v>4.842611042003125</v>
       </c>
       <c r="G486" t="n">
         <v>4.706823839714591</v>
@@ -13877,7 +13877,7 @@
         <v>4.634728988229636</v>
       </c>
       <c r="F487" t="n">
-        <v>4.832305758571839</v>
+        <v>4.840242308167575</v>
       </c>
       <c r="G487" t="n">
         <v>4.716711560720999</v>
@@ -13908,7 +13908,7 @@
         <v>4.627909672957581</v>
       </c>
       <c r="F488" t="n">
-        <v>4.820281565605037</v>
+        <v>4.817050545023591</v>
       </c>
       <c r="G488" t="n">
         <v>4.71760561531788</v>
@@ -13972,7 +13972,7 @@
         <v>4.630837932736669</v>
       </c>
       <c r="F490" t="n">
-        <v>4.773223770984341</v>
+        <v>4.772378104971998</v>
       </c>
       <c r="G490" t="n">
         <v>4.721173861744398</v>
@@ -14003,7 +14003,7 @@
         <v>4.637637376125593</v>
       </c>
       <c r="F491" t="n">
-        <v>4.799914262780603</v>
+        <v>4.798266815950004</v>
       </c>
       <c r="G491" t="n">
         <v>4.721173861744398</v>
@@ -14034,7 +14034,7 @@
         <v>4.649187071404866</v>
       </c>
       <c r="F492" t="n">
-        <v>4.763881877142913</v>
+        <v>4.763028270603671</v>
       </c>
       <c r="G492" t="n">
         <v>4.730039168033961</v>
@@ -14067,7 +14067,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="F493" t="n">
-        <v>4.739701078945697</v>
+        <v>4.73707525686803</v>
       </c>
       <c r="G493" t="n">
         <v>4.720282993088596</v>
@@ -14098,7 +14098,7 @@
         <v>4.618086411254637</v>
       </c>
       <c r="F494" t="n">
-        <v>4.693181063310805</v>
+        <v>4.690430029938915</v>
       </c>
       <c r="G494" t="n">
         <v>4.719391330078114</v>
@@ -14129,7 +14129,7 @@
         <v>4.619073091157083</v>
       </c>
       <c r="F495" t="n">
-        <v>4.703203926259457</v>
+        <v>4.69866052907543</v>
       </c>
       <c r="G495" t="n">
         <v>4.718498871295094</v>
@@ -14162,7 +14162,7 @@
         <v>4.645351975620923</v>
       </c>
       <c r="F496" t="n">
-        <v>4.722953221644475</v>
+        <v>4.71760561531788</v>
       </c>
       <c r="G496" t="n">
         <v>4.729156165769083</v>
@@ -14193,7 +14193,7 @@
         <v>4.640537329825382</v>
       </c>
       <c r="F497" t="n">
-        <v>4.728272383122075</v>
+        <v>4.722953221644475</v>
       </c>
       <c r="G497" t="n">
         <v>4.714024590900173</v>
@@ -14224,7 +14224,7 @@
         <v>4.650143551630823</v>
       </c>
       <c r="F498" t="n">
-        <v>4.694096395182493</v>
+        <v>4.688591794127164</v>
       </c>
       <c r="G498" t="n">
         <v>4.719391330078114</v>
@@ -14257,7 +14257,7 @@
         <v>4.644390899141372</v>
       </c>
       <c r="F499" t="n">
-        <v>4.696837374513915</v>
+        <v>4.681204872264089</v>
       </c>
       <c r="G499" t="n">
         <v>4.722953221644475</v>
@@ -14287,7 +14287,9 @@
       <c r="E500" t="n">
         <v>4.650143551630823</v>
       </c>
-      <c r="F500" t="inlineStr"/>
+      <c r="F500" t="n">
+        <v>4.677490847567717</v>
+      </c>
       <c r="G500" t="n">
         <v>4.714024590900173</v>
       </c>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14320,7 +14320,7 @@
       <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
-        <v>4.651194624299371</v>
+        <v>4.651481088851342</v>
       </c>
       <c r="J501" t="n">
         <v>4.363913651397029</v>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -13010,7 +13010,7 @@
         <v>45016</v>
       </c>
       <c r="B460" t="n">
-        <v>12.69449927435268</v>
+        <v>12.69331127028978</v>
       </c>
       <c r="C460" t="n">
         <v>2.9105652</v>
@@ -13105,7 +13105,7 @@
         <v>45107</v>
       </c>
       <c r="B463" t="n">
-        <v>12.69593711116222</v>
+        <v>12.69454836043127</v>
       </c>
       <c r="C463" t="n">
         <v>3.5358636</v>
@@ -13200,7 +13200,7 @@
         <v>45199</v>
       </c>
       <c r="B466" t="n">
-        <v>12.7038039111649</v>
+        <v>12.70292509765854</v>
       </c>
       <c r="C466" t="n">
         <v>3.8800476</v>
@@ -13295,7 +13295,7 @@
         <v>45291</v>
       </c>
       <c r="B469" t="n">
-        <v>12.71165756074105</v>
+        <v>12.71116285319663</v>
       </c>
       <c r="C469" t="n">
         <v>3.9348947</v>
@@ -13390,7 +13390,7 @@
         <v>45382</v>
       </c>
       <c r="B472" t="n">
-        <v>12.72272724774461</v>
+        <v>12.72400594978309</v>
       </c>
       <c r="C472" t="n">
         <v>3.9231</v>
@@ -13485,7 +13485,7 @@
         <v>45473</v>
       </c>
       <c r="B475" t="n">
-        <v>12.7318745626749</v>
+        <v>12.7333364195522</v>
       </c>
       <c r="C475" t="n">
         <v>3.7245</v>
@@ -13580,7 +13580,7 @@
         <v>45565</v>
       </c>
       <c r="B478" t="n">
-        <v>12.73949698389434</v>
+        <v>12.74112931196489</v>
       </c>
       <c r="C478" t="n">
         <v>3.4337143</v>
@@ -13675,7 +13675,7 @@
         <v>45657</v>
       </c>
       <c r="B481" t="n">
-        <v>12.7476001073437</v>
+        <v>12.74766992796292</v>
       </c>
       <c r="C481" t="n">
         <v>2.8246</v>
@@ -13770,7 +13770,7 @@
         <v>45747</v>
       </c>
       <c r="B484" t="n">
-        <v>12.75306914410922</v>
+        <v>12.75249608150816</v>
       </c>
       <c r="C484" t="n">
         <v>2.4424286</v>
@@ -13865,7 +13865,7 @@
         <v>45838</v>
       </c>
       <c r="B487" t="n">
-        <v>12.76018761739456</v>
+        <v>12.75915571306601</v>
       </c>
       <c r="C487" t="n">
         <v>1.983619</v>
@@ -13960,7 +13960,7 @@
         <v>45930</v>
       </c>
       <c r="B490" t="n">
-        <v>12.7661397601738</v>
+        <v>12.76481662497956</v>
       </c>
       <c r="C490" t="n">
         <v>2.0272727</v>
@@ -14055,7 +14055,7 @@
         <v>46022</v>
       </c>
       <c r="B493" t="n">
-        <v>12.77378698010285</v>
+        <v>12.77208507412512</v>
       </c>
       <c r="C493" t="n">
         <v>2.0484286</v>
@@ -14150,7 +14150,7 @@
         <v>46112</v>
       </c>
       <c r="B496" t="n">
-        <v>12.78000545406039</v>
+        <v>12.77836488947364</v>
       </c>
       <c r="C496" t="n">
         <v>2.1094091</v>
@@ -14245,7 +14245,7 @@
         <v>46203</v>
       </c>
       <c r="B499" t="n">
-        <v>12.7869130184882</v>
+        <v>12.78518569201263</v>
       </c>
       <c r="C499" t="n">
         <v>2.339</v>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:K502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,7 +2199,7 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>4.275276264727001</v>
+        <v>4.273884476054178</v>
       </c>
       <c r="E95" t="n">
         <v>4.51852237926242</v>
@@ -4717,7 +4717,7 @@
         <v>4.7558</v>
       </c>
       <c r="D195" t="n">
-        <v>4.707726774313183</v>
+        <v>4.708628894356321</v>
       </c>
       <c r="E195" t="n">
         <v>4.779963476361254</v>
@@ -6746,7 +6746,7 @@
         <v>3.335381</v>
       </c>
       <c r="D262" t="n">
-        <v>4.659658371272161</v>
+        <v>4.658710952916121</v>
       </c>
       <c r="E262" t="n">
         <v>4.859036909945142</v>
@@ -9722,7 +9722,7 @@
         <v>0.2050435</v>
       </c>
       <c r="D356" t="n">
-        <v>4.61512051684126</v>
+        <v>4.616110126026426</v>
       </c>
       <c r="E356" t="n">
         <v>4.536891345234797</v>
@@ -10387,7 +10387,7 @@
         <v>-0.2491905</v>
       </c>
       <c r="D377" t="n">
-        <v>4.653960350157523</v>
+        <v>4.654912277882906</v>
       </c>
       <c r="E377" t="n">
         <v>4.613138355637268</v>
@@ -11306,7 +11306,7 @@
         <v>-0.31885</v>
       </c>
       <c r="D406" t="n">
-        <v>4.65586330030361</v>
+        <v>4.654912277882906</v>
       </c>
       <c r="E406" t="n">
         <v>4.621043535144381</v>
@@ -11686,7 +11686,7 @@
         <v>-0.4175714</v>
       </c>
       <c r="D418" t="n">
-        <v>4.638604962074329</v>
+        <v>4.637637376125593</v>
       </c>
       <c r="E418" t="n">
         <v>4.625952725170619</v>
@@ -12446,7 +12446,7 @@
         <v>-0.5450455</v>
       </c>
       <c r="D442" t="n">
-        <v>4.695924549256556</v>
+        <v>4.695010889987881</v>
       </c>
       <c r="E442" t="n">
         <v>4.598145571051127</v>
@@ -12857,7 +12857,7 @@
         <v>1.4276667</v>
       </c>
       <c r="D455" t="n">
-        <v>4.585987366571318</v>
+        <v>4.584967478670572</v>
       </c>
       <c r="E455" t="n">
         <v>4.620058798481842</v>
@@ -13586,7 +13586,7 @@
         <v>3.4337143</v>
       </c>
       <c r="D478" t="n">
-        <v>4.674696248636701</v>
+        <v>4.673762977453703</v>
       </c>
       <c r="E478" t="n">
         <v>4.616110126026426</v>
@@ -13838,7 +13838,7 @@
         <v>2.0872381</v>
       </c>
       <c r="D486" t="n">
-        <v>4.633757642840004</v>
+        <v>4.634728988229636</v>
       </c>
       <c r="E486" t="n">
         <v>4.622027303054514</v>
@@ -13966,7 +13966,7 @@
         <v>2.0272727</v>
       </c>
       <c r="D490" t="n">
-        <v>4.647271362006727</v>
+        <v>4.646312129319266</v>
       </c>
       <c r="E490" t="n">
         <v>4.630837932736669</v>
@@ -13997,7 +13997,7 @@
         <v>2.0344348</v>
       </c>
       <c r="D491" t="n">
-        <v>4.641502115235482</v>
+        <v>4.640537329825382</v>
       </c>
       <c r="E491" t="n">
         <v>4.637637376125593</v>
@@ -14251,7 +14251,7 @@
         <v>2.339</v>
       </c>
       <c r="D499" t="n">
-        <v>4.638604962074329</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="E499" t="n">
         <v>4.644390899141372</v>
@@ -14327,6 +14327,23 @@
       </c>
       <c r="K501" t="inlineStr"/>
     </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="n">
+        <v>4.658710952916121</v>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>4.658710952916121</v>
+        <v>4.657762636107262</v>
       </c>
       <c r="H187" t="n">
         <v>11.9</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>4.725616339063959</v>
+        <v>4.726502471155617</v>
       </c>
       <c r="H205" t="n">
         <v>10.7</v>
@@ -6216,7 +6216,7 @@
         <v>5.376203905205108</v>
       </c>
       <c r="G245" t="n">
-        <v>4.801558999993482</v>
+        <v>4.800736969532067</v>
       </c>
       <c r="H245" t="n">
         <v>9.699999999999999</v>
@@ -6596,7 +6596,7 @@
         <v>5.41565585896527</v>
       </c>
       <c r="G257" t="n">
-        <v>4.805659046737495</v>
+        <v>4.806477042693126</v>
       </c>
       <c r="H257" t="n">
         <v>8.6</v>
@@ -7102,7 +7102,7 @@
         <v>5.358471289367784</v>
       </c>
       <c r="G273" t="n">
-        <v>4.847331743138063</v>
+        <v>4.846546505563361</v>
       </c>
       <c r="H273" t="n">
         <v>8.300000000000001</v>
@@ -7325,7 +7325,7 @@
         <v>5.24649761781824</v>
       </c>
       <c r="G280" t="n">
-        <v>4.794963757620747</v>
+        <v>4.795790545596741</v>
       </c>
       <c r="H280" t="n">
         <v>9.5</v>
@@ -7546,7 +7546,7 @@
         <v>5.132262782217954</v>
       </c>
       <c r="G287" t="n">
-        <v>4.763028270603671</v>
+        <v>4.762173934797756</v>
       </c>
       <c r="H287" t="n">
         <v>12.9</v>
@@ -9636,7 +9636,7 @@
         <v>4.841032509710076</v>
       </c>
       <c r="G353" t="n">
-        <v>4.507557357121091</v>
+        <v>4.506454213048934</v>
       </c>
       <c r="H353" t="n">
         <v>24.8</v>
@@ -10681,7 +10681,7 @@
         <v>4.814620410170298</v>
       </c>
       <c r="G386" t="n">
-        <v>4.592084946439436</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="H386" t="n">
         <v>18.3</v>
@@ -11410,7 +11410,7 @@
         <v>4.832305758571839</v>
       </c>
       <c r="G409" t="n">
-        <v>4.61512051684126</v>
+        <v>4.616110126026426</v>
       </c>
       <c r="H409" t="n">
         <v>14.4</v>
@@ -13277,7 +13277,7 @@
         <v>4.574710978503383</v>
       </c>
       <c r="G468" t="n">
-        <v>4.665324108807838</v>
+        <v>4.666265285347902</v>
       </c>
       <c r="H468" t="n">
         <v>12</v>
@@ -13562,7 +13562,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="G477" t="n">
-        <v>4.672828834461906</v>
+        <v>4.673762977453703</v>
       </c>
       <c r="H477" t="n">
         <v>11.3</v>
@@ -13626,7 +13626,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="G479" t="n">
-        <v>4.683056724645162</v>
+        <v>4.683981366412381</v>
       </c>
       <c r="H479" t="n">
         <v>10.9</v>
@@ -13657,7 +13657,7 @@
         <v>4.607168188650764</v>
       </c>
       <c r="G480" t="n">
-        <v>4.671893818030999</v>
+        <v>4.672828834461906</v>
       </c>
       <c r="H480" t="n">
         <v>10.8</v>
@@ -13911,7 +13911,7 @@
         <v>4.817050545023591</v>
       </c>
       <c r="G488" t="n">
-        <v>4.71760561531788</v>
+        <v>4.716711560720999</v>
       </c>
       <c r="H488" t="n">
         <v>10.6</v>
@@ -13942,7 +13942,7 @@
         <v>4.780802754631249</v>
       </c>
       <c r="G489" t="n">
-        <v>4.71760561531788</v>
+        <v>4.719391330078114</v>
       </c>
       <c r="H489" t="n">
         <v>10.5</v>
@@ -14006,7 +14006,7 @@
         <v>4.798266815950004</v>
       </c>
       <c r="G491" t="n">
-        <v>4.721173861744398</v>
+        <v>4.722063937459591</v>
       </c>
       <c r="H491" t="n">
         <v>10.2</v>
@@ -14196,7 +14196,7 @@
         <v>4.722953221644475</v>
       </c>
       <c r="G497" t="n">
-        <v>4.714024590900173</v>
+        <v>4.713127327493184</v>
       </c>
       <c r="H497" t="n">
         <v>10.2</v>
@@ -14260,7 +14260,7 @@
         <v>4.681204872264089</v>
       </c>
       <c r="G499" t="n">
-        <v>4.722953221644475</v>
+        <v>4.722063937459591</v>
       </c>
       <c r="H499" t="n">
         <v>10.1</v>
@@ -14291,7 +14291,7 @@
         <v>4.677490847567717</v>
       </c>
       <c r="G500" t="n">
-        <v>4.714024590900173</v>
+        <v>4.712229258281499</v>
       </c>
       <c r="H500" t="n">
         <v>10</v>
@@ -14317,7 +14317,9 @@
       </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
+      <c r="G501" t="n">
+        <v>4.71492104994721</v>
+      </c>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
         <v>4.651481088851342</v>
@@ -14332,7 +14334,9 @@
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
-      <c r="C502" t="inlineStr"/>
+      <c r="C502" t="n">
+        <v>2.6350455</v>
+      </c>
       <c r="D502" t="n">
         <v>4.658710952916121</v>
       </c>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -12838,7 +12838,7 @@
         <v>4.632785353021065</v>
       </c>
       <c r="H454" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="I454" t="n">
         <v>4.53066213381303</v>
@@ -14320,7 +14320,9 @@
       <c r="G501" t="n">
         <v>4.71492104994721</v>
       </c>
-      <c r="H501" t="inlineStr"/>
+      <c r="H501" t="n">
+        <v>10</v>
+      </c>
       <c r="I501" t="n">
         <v>4.651481088851342</v>
       </c>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14346,7 +14346,9 @@
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
+      <c r="I502" t="n">
+        <v>4.657952371427061</v>
+      </c>
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>
     </row>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -2160,7 +2160,7 @@
         <v>4.356708826689592</v>
       </c>
       <c r="E93" t="n">
-        <v>4.533674184283021</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
@@ -2244,7 +2244,7 @@
         <v>4.194189897191817</v>
       </c>
       <c r="E97" t="n">
-        <v>4.476199804691132</v>
+        <v>4.477336814478207</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
@@ -2914,7 +2914,7 @@
         <v>4.547541073151455</v>
       </c>
       <c r="E127" t="n">
-        <v>4.627909672957581</v>
+        <v>4.626931677769604</v>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
         <v>4.528289141652134</v>
       </c>
       <c r="E132" t="n">
-        <v>4.606169686321175</v>
+        <v>4.607168188650764</v>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
         <v>4.564348191467836</v>
       </c>
       <c r="E140" t="n">
-        <v>4.59511985013459</v>
+        <v>4.596129441335942</v>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
         <v>4.742320024135325</v>
       </c>
       <c r="E187" t="n">
-        <v>4.796616650559047</v>
+        <v>4.795790545596741</v>
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
@@ -5403,7 +5403,7 @@
         <v>4.636668853047462</v>
       </c>
       <c r="E218" t="n">
-        <v>4.77912349311153</v>
+        <v>4.778282803696737</v>
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
@@ -5908,7 +5908,7 @@
         <v>4.66814498514948</v>
       </c>
       <c r="E235" t="n">
-        <v>4.816241156068032</v>
+        <v>4.815431111471288</v>
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
@@ -8015,7 +8015,7 @@
         <v>4.472780997942346</v>
       </c>
       <c r="E302" t="n">
-        <v>4.606169686321175</v>
+        <v>4.605170185988092</v>
       </c>
       <c r="F302" t="n">
         <v>4.998562712861986</v>
@@ -8554,7 +8554,7 @@
         <v>4.52720864451838</v>
       </c>
       <c r="E319" t="n">
-        <v>4.609162207257629</v>
+        <v>4.61015772749913</v>
       </c>
       <c r="F319" t="n">
         <v>4.622027303054514</v>
@@ -8585,7 +8585,7 @@
         <v>4.500920164614292</v>
       </c>
       <c r="E320" t="n">
-        <v>4.616110126026426</v>
+        <v>4.61512051684126</v>
       </c>
       <c r="F320" t="n">
         <v>4.636668853047462</v>
@@ -8996,7 +8996,7 @@
         <v>4.387014176184921</v>
       </c>
       <c r="E333" t="n">
-        <v>4.562262684976814</v>
+        <v>4.561218298458908</v>
       </c>
       <c r="F333" t="n">
         <v>4.611152257665639</v>
@@ -9219,7 +9219,7 @@
         <v>4.439115601658009</v>
       </c>
       <c r="E340" t="n">
-        <v>4.530446639792155</v>
+        <v>4.529368472571809</v>
       </c>
       <c r="F340" t="n">
         <v>4.548599834499697</v>
@@ -9314,7 +9314,7 @@
         <v>4.495355319980884</v>
       </c>
       <c r="E343" t="n">
-        <v>4.531523645819793</v>
+        <v>4.532599493153256</v>
       </c>
       <c r="F343" t="n">
         <v>4.622027303054514</v>
@@ -10390,7 +10390,7 @@
         <v>4.654912277882906</v>
       </c>
       <c r="E377" t="n">
-        <v>4.613138355637268</v>
+        <v>4.612145799724517</v>
       </c>
       <c r="F377" t="n">
         <v>4.838660029356445</v>
@@ -11846,7 +11846,7 @@
         <v>4.642465970731788</v>
       </c>
       <c r="E423" t="n">
-        <v>4.644390899141372</v>
+        <v>4.645351975620923</v>
       </c>
       <c r="F423" t="n">
         <v>4.740574822994295</v>
@@ -12321,7 +12321,7 @@
         <v>4.654912277882906</v>
       </c>
       <c r="E438" t="n">
-        <v>4.600157644164547</v>
+        <v>4.601162164590552</v>
       </c>
       <c r="F438" t="n">
         <v>4.626931677769604</v>
@@ -12796,7 +12796,7 @@
         <v>4.574710978503383</v>
       </c>
       <c r="E453" t="n">
-        <v>4.639571612705423</v>
+        <v>4.640537329825382</v>
       </c>
       <c r="F453" t="n">
         <v>4.537961436294641</v>
@@ -13114,7 +13114,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="E463" t="n">
-        <v>4.614129927359564</v>
+        <v>4.613138355637268</v>
       </c>
       <c r="F463" t="n">
         <v>4.561218298458908</v>
@@ -13494,7 +13494,7 @@
         <v>4.627909672957581</v>
       </c>
       <c r="E475" t="n">
-        <v>4.61512051684126</v>
+        <v>4.614129927359564</v>
       </c>
       <c r="F475" t="n">
         <v>4.574710978503383</v>
@@ -13525,7 +13525,7 @@
         <v>4.644390899141372</v>
       </c>
       <c r="E476" t="n">
-        <v>4.604169685654508</v>
+        <v>4.603168183317418</v>
       </c>
       <c r="F476" t="n">
         <v>4.609162207257629</v>
@@ -13556,7 +13556,7 @@
         <v>4.654912277882906</v>
       </c>
       <c r="E477" t="n">
-        <v>4.596129441335942</v>
+        <v>4.597138014290827</v>
       </c>
       <c r="F477" t="n">
         <v>4.588024027153121</v>
@@ -13841,7 +13841,7 @@
         <v>4.634728988229636</v>
       </c>
       <c r="E486" t="n">
-        <v>4.622027303054514</v>
+        <v>4.621043535144381</v>
       </c>
       <c r="F486" t="n">
         <v>4.842611042003125</v>
@@ -13874,7 +13874,7 @@
         <v>4.621043535144381</v>
       </c>
       <c r="E487" t="n">
-        <v>4.634728988229636</v>
+        <v>4.633757642840004</v>
       </c>
       <c r="F487" t="n">
         <v>4.840242308167575</v>
@@ -13905,7 +13905,7 @@
         <v>4.628886712605407</v>
       </c>
       <c r="E488" t="n">
-        <v>4.627909672957581</v>
+        <v>4.625952725170619</v>
       </c>
       <c r="F488" t="n">
         <v>4.817050545023591</v>
@@ -13936,7 +13936,7 @@
         <v>4.619073091157083</v>
       </c>
       <c r="E489" t="n">
-        <v>4.625952725170619</v>
+        <v>4.627909672957581</v>
       </c>
       <c r="F489" t="n">
         <v>4.780802754631249</v>
@@ -13969,7 +13969,7 @@
         <v>4.646312129319266</v>
       </c>
       <c r="E490" t="n">
-        <v>4.630837932736669</v>
+        <v>4.631812116934513</v>
       </c>
       <c r="F490" t="n">
         <v>4.772378104971998</v>
@@ -14000,7 +14000,7 @@
         <v>4.640537329825382</v>
       </c>
       <c r="E491" t="n">
-        <v>4.637637376125593</v>
+        <v>4.638604962074329</v>
       </c>
       <c r="F491" t="n">
         <v>4.798266815950004</v>
@@ -14126,7 +14126,7 @@
         <v>4.663439094112067</v>
       </c>
       <c r="E495" t="n">
-        <v>4.619073091157083</v>
+        <v>4.618086411254637</v>
       </c>
       <c r="F495" t="n">
         <v>4.69866052907543</v>
@@ -14190,7 +14190,7 @@
         <v>4.631812116934513</v>
       </c>
       <c r="E497" t="n">
-        <v>4.640537329825382</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="F497" t="n">
         <v>4.722953221644475</v>
@@ -14221,7 +14221,7 @@
         <v>4.631812116934513</v>
       </c>
       <c r="E498" t="n">
-        <v>4.650143551630823</v>
+        <v>4.649187071404866</v>
       </c>
       <c r="F498" t="n">
         <v>4.688591794127164</v>
@@ -14315,7 +14315,9 @@
       <c r="D501" t="n">
         <v>4.625952725170619</v>
       </c>
-      <c r="E501" t="inlineStr"/>
+      <c r="E501" t="n">
+        <v>4.642465970731788</v>
+      </c>
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="n">
         <v>4.71492104994721</v>
@@ -14349,7 +14351,9 @@
       <c r="I502" t="n">
         <v>4.657952371427061</v>
       </c>
-      <c r="J502" t="inlineStr"/>
+      <c r="J502" t="n">
+        <v>4.596689494135473</v>
+      </c>
       <c r="K502" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,24 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,64 +421,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>GDPyoy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>EURIBOR 3M</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EcSent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CONSindex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HICP</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Brent</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>STOXX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -507,7 +493,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -522,7 +508,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -537,7 +523,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -552,7 +538,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -567,7 +553,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -582,7 +568,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -597,7 +583,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -612,7 +598,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -627,7 +613,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -642,7 +628,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -657,7 +643,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -672,7 +658,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -687,7 +673,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -702,7 +688,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -717,7 +703,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -734,7 +720,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -751,7 +737,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -768,7 +754,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -785,7 +771,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -802,7 +788,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -819,7 +805,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -836,7 +822,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -853,7 +839,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -870,7 +856,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -887,7 +873,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -904,7 +890,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -921,7 +907,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -940,7 +926,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -959,7 +945,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -978,7 +964,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -997,7 +983,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1016,7 +1002,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1035,7 +1021,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1054,7 +1040,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1073,7 +1059,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1092,7 +1078,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1111,7 +1097,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1130,7 +1116,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1149,7 +1135,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1168,7 +1154,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1187,7 +1173,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1206,7 +1192,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1225,7 +1211,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1244,7 +1230,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1263,7 +1249,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1282,7 +1268,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1301,7 +1287,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1320,7 +1306,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1339,7 +1325,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1358,7 +1344,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1377,7 +1363,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1396,7 +1382,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1415,7 +1401,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1434,7 +1420,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1453,7 +1439,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1472,7 +1458,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1491,7 +1477,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1510,7 +1496,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1529,7 +1515,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -1548,7 +1534,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1567,7 +1553,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1586,7 +1572,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -1605,7 +1591,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1624,7 +1610,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1643,7 +1629,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1662,7 +1648,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1681,7 +1667,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1700,7 +1686,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1719,7 +1705,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1738,7 +1724,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1757,7 +1743,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1776,7 +1762,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1795,7 +1781,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1814,7 +1800,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1833,7 +1819,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1852,7 +1838,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1871,7 +1857,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -1890,7 +1876,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -1909,7 +1895,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -1928,7 +1914,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -1947,7 +1933,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -1966,7 +1952,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -1985,7 +1971,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2004,7 +1990,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2025,7 +2011,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2046,7 +2032,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -2067,7 +2053,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2088,7 +2074,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2109,7 +2095,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -2130,7 +2116,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2151,7 +2137,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2172,7 +2158,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -2193,7 +2179,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2214,7 +2200,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2235,7 +2221,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -2256,7 +2242,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2277,7 +2263,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2298,7 +2284,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -2319,7 +2305,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2340,7 +2326,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2361,7 +2347,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -2382,7 +2368,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2403,7 +2389,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2424,7 +2410,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2445,7 +2431,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2466,7 +2452,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2487,7 +2473,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -2508,7 +2494,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2531,7 +2517,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2554,7 +2540,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -2577,7 +2563,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2600,7 +2586,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -2623,7 +2609,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -2646,7 +2632,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2669,7 +2655,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2692,7 +2678,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2715,7 +2701,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -2738,7 +2724,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -2761,7 +2747,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -2784,7 +2770,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2807,7 +2793,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -2830,7 +2816,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="n">
@@ -2855,7 +2841,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -2878,7 +2864,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -2901,7 +2887,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="n">
@@ -2926,7 +2912,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -2949,7 +2935,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -2972,7 +2958,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="n">
@@ -2997,7 +2983,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -3020,7 +3006,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -3043,7 +3029,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="n">
@@ -3068,7 +3054,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -3093,7 +3079,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -3118,7 +3104,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -3145,7 +3131,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3170,7 +3156,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3195,7 +3181,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -3222,7 +3208,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3247,7 +3233,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3272,7 +3258,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -3299,7 +3285,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3324,7 +3310,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3349,7 +3335,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -3376,7 +3362,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3401,7 +3387,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3426,7 +3412,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -3453,7 +3439,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3478,7 +3464,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -3503,7 +3489,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -3530,7 +3516,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3555,7 +3541,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3580,7 +3566,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -3607,7 +3593,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -3632,7 +3618,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -3657,7 +3643,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -3684,7 +3670,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -3709,7 +3695,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -3734,7 +3720,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -3761,7 +3747,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -3786,7 +3772,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -3811,7 +3797,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -3838,7 +3824,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -3863,7 +3849,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -3888,7 +3874,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -3915,7 +3901,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -3940,7 +3926,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -3965,7 +3951,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -3992,7 +3978,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -4019,7 +4005,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -4046,7 +4032,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -4075,7 +4061,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -4102,7 +4088,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -4129,7 +4115,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -4158,7 +4144,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -4185,7 +4171,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -4212,7 +4198,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -4241,7 +4227,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4268,7 +4254,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4295,7 +4281,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -4324,7 +4310,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4353,7 +4339,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4382,7 +4368,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -4413,7 +4399,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4442,7 +4428,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4471,7 +4457,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -4502,7 +4488,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -4531,7 +4517,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -4560,7 +4546,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -4591,7 +4577,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -4620,7 +4606,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -4649,7 +4635,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -4680,7 +4666,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -4709,7 +4695,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -4738,7 +4724,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -4769,7 +4755,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -4798,7 +4784,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -4827,7 +4813,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -4858,7 +4844,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -4887,7 +4873,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -4916,7 +4902,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -4947,7 +4933,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -4976,7 +4962,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -5005,7 +4991,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -5036,7 +5022,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -5065,7 +5051,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -5094,7 +5080,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -5125,7 +5111,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -5154,7 +5140,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -5183,7 +5169,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -5214,7 +5200,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -5243,7 +5229,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -5272,7 +5258,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -5303,7 +5289,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -5332,7 +5318,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -5361,7 +5347,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -5392,7 +5378,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -5421,7 +5407,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -5450,7 +5436,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -5481,7 +5467,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -5510,7 +5496,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -5539,7 +5525,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -5570,7 +5556,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -5599,7 +5585,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -5628,7 +5614,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -5659,7 +5645,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -5688,7 +5674,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -5717,7 +5703,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -5748,7 +5734,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -5777,7 +5763,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -5806,7 +5792,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -5837,7 +5823,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -5866,7 +5852,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -5895,7 +5881,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -5926,7 +5912,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -5955,7 +5941,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -5984,7 +5970,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -6015,7 +6001,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -6044,7 +6030,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -6073,7 +6059,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -6104,7 +6090,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -6135,7 +6121,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -6166,7 +6152,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -6199,7 +6185,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -6230,7 +6216,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -6261,7 +6247,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -6294,7 +6280,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -6325,7 +6311,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -6356,7 +6342,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -6389,7 +6375,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -6420,7 +6406,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -6451,7 +6437,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -6484,7 +6470,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -6515,7 +6501,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -6546,7 +6532,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -6579,7 +6565,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -6610,7 +6596,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -6641,7 +6627,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -6674,7 +6660,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -6705,7 +6691,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -6736,7 +6722,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -6769,7 +6755,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -6800,7 +6786,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -6831,7 +6817,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -6864,7 +6850,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -6895,7 +6881,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -6926,7 +6912,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -6959,7 +6945,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -6990,7 +6976,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -7021,7 +7007,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -7054,7 +7040,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -7085,7 +7071,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -7116,7 +7102,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -7149,7 +7135,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -7180,7 +7166,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -7211,7 +7197,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -7244,7 +7230,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -7275,7 +7261,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -7306,7 +7292,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -7339,7 +7325,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -7370,7 +7356,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -7401,7 +7387,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -7434,7 +7420,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -7465,7 +7451,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -7496,7 +7482,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -7529,7 +7515,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -7560,7 +7546,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -7591,7 +7577,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -7624,7 +7610,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -7655,7 +7641,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -7686,7 +7672,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -7719,7 +7705,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -7750,7 +7736,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -7781,7 +7767,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -7814,7 +7800,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -7845,7 +7831,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -7876,7 +7862,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -7909,7 +7895,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -7940,7 +7926,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -7971,7 +7957,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -8004,7 +7990,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -8035,7 +8021,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -8066,7 +8052,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -8099,7 +8085,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -8130,7 +8116,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -8161,7 +8147,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -8194,7 +8180,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -8225,7 +8211,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -8256,7 +8242,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -8289,7 +8275,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -8320,7 +8306,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -8351,7 +8337,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -8384,7 +8370,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -8415,7 +8401,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -8446,7 +8432,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -8479,7 +8465,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -8510,7 +8496,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -8541,7 +8527,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -8574,7 +8560,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -8605,7 +8591,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -8636,7 +8622,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -8669,7 +8655,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -8700,7 +8686,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -8731,7 +8717,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -8764,7 +8750,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -8795,7 +8781,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -8826,7 +8812,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -8859,7 +8845,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -8890,7 +8876,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -8921,7 +8907,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -8954,7 +8940,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -8985,7 +8971,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -9016,7 +9002,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -9049,7 +9035,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -9080,7 +9066,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -9111,7 +9097,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -9144,7 +9130,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -9175,7 +9161,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -9206,7 +9192,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -9239,7 +9225,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -9270,7 +9256,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -9301,7 +9287,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -9334,7 +9320,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -9365,7 +9351,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -9396,7 +9382,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -9429,7 +9415,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -9460,7 +9446,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -9491,7 +9477,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -9524,7 +9510,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -9555,7 +9541,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -9586,7 +9572,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -9619,7 +9605,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -9650,7 +9636,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -9681,7 +9667,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -9714,7 +9700,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -9745,7 +9731,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -9776,7 +9762,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -9809,7 +9795,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -9840,7 +9826,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -9871,7 +9857,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -9904,7 +9890,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -9935,7 +9921,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -9966,7 +9952,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -9999,7 +9985,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -10030,7 +10016,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -10061,7 +10047,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -10094,7 +10080,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -10125,7 +10111,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -10156,7 +10142,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -10189,7 +10175,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -10220,7 +10206,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -10251,7 +10237,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -10284,7 +10270,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -10315,7 +10301,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -10346,7 +10332,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -10379,7 +10365,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -10410,7 +10396,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -10441,7 +10427,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -10474,7 +10460,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -10505,7 +10491,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -10536,7 +10522,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -10569,7 +10555,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -10600,7 +10586,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -10631,7 +10617,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -10664,7 +10650,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -10695,7 +10681,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -10726,7 +10712,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -10759,7 +10745,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -10790,7 +10776,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -10821,7 +10807,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -10854,7 +10840,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -10885,7 +10871,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -10916,7 +10902,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -10949,7 +10935,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -10980,7 +10966,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -11011,7 +10997,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -11044,7 +11030,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -11075,7 +11061,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -11106,7 +11092,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -11139,7 +11125,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -11170,7 +11156,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -11201,7 +11187,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -11234,7 +11220,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -11265,7 +11251,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -11296,7 +11282,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -11329,7 +11315,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -11360,7 +11346,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -11391,7 +11377,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -11424,7 +11410,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -11455,7 +11441,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -11486,7 +11472,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -11519,7 +11505,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -11550,7 +11536,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -11581,7 +11567,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -11614,7 +11600,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -11645,7 +11631,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -11676,7 +11662,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -11709,7 +11695,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -11740,7 +11726,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -11771,7 +11757,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -11804,7 +11790,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -11835,7 +11821,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -11866,7 +11852,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -11899,7 +11885,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -11930,7 +11916,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -11961,7 +11947,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -11994,7 +11980,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -12025,7 +12011,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -12056,7 +12042,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -12089,7 +12075,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -12120,7 +12106,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -12151,7 +12137,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -12184,7 +12170,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -12215,7 +12201,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -12246,7 +12232,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -12279,7 +12265,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -12310,7 +12296,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -12341,7 +12327,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -12374,7 +12360,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -12405,7 +12391,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -12436,7 +12422,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -12469,7 +12455,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -12500,7 +12486,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -12531,7 +12517,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -12564,7 +12550,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -12595,7 +12581,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -12626,7 +12612,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -12659,7 +12645,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -12690,7 +12676,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -12721,7 +12707,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -12754,7 +12740,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -12785,7 +12771,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -12816,7 +12802,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -12849,7 +12835,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -12880,7 +12866,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -12911,7 +12897,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -12944,7 +12930,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -12975,7 +12961,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -13006,7 +12992,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -13039,7 +13025,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -13070,7 +13056,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -13101,7 +13087,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -13134,7 +13120,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -13165,7 +13151,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -13196,7 +13182,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -13229,7 +13215,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -13260,7 +13246,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -13291,7 +13277,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -13324,7 +13310,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -13355,7 +13341,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -13386,7 +13372,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -13419,7 +13405,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -13450,7 +13436,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -13481,7 +13467,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -13514,7 +13500,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -13545,7 +13531,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -13576,7 +13562,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -13609,7 +13595,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -13640,7 +13626,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -13671,7 +13657,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -13704,7 +13690,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -13718,7 +13704,7 @@
         <v>4.619073091157083</v>
       </c>
       <c r="F482" t="n">
-        <v>4.887337077751762</v>
+        <v>4.886582645426277</v>
       </c>
       <c r="G482" t="n">
         <v>4.683056724645162</v>
@@ -13735,7 +13721,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -13749,7 +13735,7 @@
         <v>4.628886712605407</v>
       </c>
       <c r="F483" t="n">
-        <v>4.880526608749236</v>
+        <v>4.881285622068407</v>
       </c>
       <c r="G483" t="n">
         <v>4.696837374513915</v>
@@ -13766,7 +13752,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -13782,7 +13768,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="F484" t="n">
-        <v>4.83469334426634</v>
+        <v>4.835487941050301</v>
       </c>
       <c r="G484" t="n">
         <v>4.690430029938915</v>
@@ -13799,7 +13785,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -13830,7 +13816,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -13844,7 +13830,7 @@
         <v>4.621043535144381</v>
       </c>
       <c r="F486" t="n">
-        <v>4.842611042003125</v>
+        <v>4.843399374720342</v>
       </c>
       <c r="G486" t="n">
         <v>4.706823839714591</v>
@@ -13861,7 +13847,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -13877,7 +13863,7 @@
         <v>4.633757642840004</v>
       </c>
       <c r="F487" t="n">
-        <v>4.840242308167575</v>
+        <v>4.842611042003125</v>
       </c>
       <c r="G487" t="n">
         <v>4.716711560720999</v>
@@ -13894,7 +13880,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -13908,7 +13894,7 @@
         <v>4.625952725170619</v>
       </c>
       <c r="F488" t="n">
-        <v>4.817050545023591</v>
+        <v>4.821893169499378</v>
       </c>
       <c r="G488" t="n">
         <v>4.716711560720999</v>
@@ -13925,7 +13911,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -13939,7 +13925,7 @@
         <v>4.627909672957581</v>
       </c>
       <c r="F489" t="n">
-        <v>4.780802754631249</v>
+        <v>4.767289035464526</v>
       </c>
       <c r="G489" t="n">
         <v>4.719391330078114</v>
@@ -13956,7 +13942,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -13972,7 +13958,7 @@
         <v>4.631812116934513</v>
       </c>
       <c r="F490" t="n">
-        <v>4.772378104971998</v>
+        <v>4.768988271217486</v>
       </c>
       <c r="G490" t="n">
         <v>4.721173861744398</v>
@@ -13989,7 +13975,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -14003,7 +13989,7 @@
         <v>4.638604962074329</v>
       </c>
       <c r="F491" t="n">
-        <v>4.798266815950004</v>
+        <v>4.795790545596741</v>
       </c>
       <c r="G491" t="n">
         <v>4.722063937459591</v>
@@ -14020,7 +14006,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -14034,7 +14020,7 @@
         <v>4.649187071404866</v>
       </c>
       <c r="F492" t="n">
-        <v>4.763028270603671</v>
+        <v>4.760463070394127</v>
       </c>
       <c r="G492" t="n">
         <v>4.730039168033961</v>
@@ -14051,7 +14037,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -14067,7 +14053,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="F493" t="n">
-        <v>4.73707525686803</v>
+        <v>4.736198448394496</v>
       </c>
       <c r="G493" t="n">
         <v>4.720282993088596</v>
@@ -14084,7 +14070,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -14098,7 +14084,7 @@
         <v>4.618086411254637</v>
       </c>
       <c r="F494" t="n">
-        <v>4.690430029938915</v>
+        <v>4.692264892839025</v>
       </c>
       <c r="G494" t="n">
         <v>4.719391330078114</v>
@@ -14115,7 +14101,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -14129,7 +14115,7 @@
         <v>4.618086411254637</v>
       </c>
       <c r="F495" t="n">
-        <v>4.69866052907543</v>
+        <v>4.700480365792417</v>
       </c>
       <c r="G495" t="n">
         <v>4.718498871295094</v>
@@ -14146,7 +14132,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -14162,7 +14148,7 @@
         <v>4.645351975620923</v>
       </c>
       <c r="F496" t="n">
-        <v>4.71760561531788</v>
+        <v>4.722063937459591</v>
       </c>
       <c r="G496" t="n">
         <v>4.729156165769083</v>
@@ -14179,7 +14165,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -14193,7 +14179,7 @@
         <v>4.639571612705423</v>
       </c>
       <c r="F497" t="n">
-        <v>4.722953221644475</v>
+        <v>4.730039168033961</v>
       </c>
       <c r="G497" t="n">
         <v>4.713127327493184</v>
@@ -14210,7 +14196,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -14224,7 +14210,7 @@
         <v>4.649187071404866</v>
       </c>
       <c r="F498" t="n">
-        <v>4.688591794127164</v>
+        <v>4.695924549256556</v>
       </c>
       <c r="G498" t="n">
         <v>4.719391330078114</v>
@@ -14241,7 +14227,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -14257,7 +14243,7 @@
         <v>4.644390899141372</v>
       </c>
       <c r="F499" t="n">
-        <v>4.681204872264089</v>
+        <v>4.690430029938915</v>
       </c>
       <c r="G499" t="n">
         <v>4.722063937459591</v>
@@ -14274,7 +14260,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -14288,7 +14274,7 @@
         <v>4.650143551630823</v>
       </c>
       <c r="F500" t="n">
-        <v>4.677490847567717</v>
+        <v>4.687671407499835</v>
       </c>
       <c r="G500" t="n">
         <v>4.712229258281499</v>
@@ -14305,7 +14291,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -14318,7 +14304,9 @@
       <c r="E501" t="n">
         <v>4.642465970731788</v>
       </c>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" t="n">
+        <v>4.695010889987881</v>
+      </c>
       <c r="G501" t="n">
         <v>4.71492104994721</v>
       </c>
@@ -14334,7 +14322,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -14349,7 +14337,7 @@
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="n">
-        <v>4.657952371427061</v>
+        <v>4.657762636107262</v>
       </c>
       <c r="J502" t="n">
         <v>4.596689494135473</v>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +48,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,64 +435,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>GDPyoy</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>EURIBOR 3M</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EcSent</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CONSindex</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HICP</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Brent</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>STOXX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -493,7 +507,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -508,7 +522,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -523,7 +537,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -538,7 +552,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -553,7 +567,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -568,7 +582,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -583,7 +597,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -598,7 +612,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -613,7 +627,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -628,7 +642,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -643,7 +657,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -658,7 +672,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -673,7 +687,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -688,7 +702,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -703,7 +717,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -720,7 +734,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -737,7 +751,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -754,7 +768,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -771,7 +785,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -788,7 +802,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -805,7 +819,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -822,7 +836,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -839,7 +853,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -856,7 +870,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -873,7 +887,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -890,7 +904,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -907,7 +921,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -926,7 +940,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -945,7 +959,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -964,7 +978,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -983,7 +997,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1002,7 +1016,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1021,7 +1035,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1040,7 +1054,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1059,7 +1073,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1078,7 +1092,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1097,7 +1111,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1116,7 +1130,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1135,7 +1149,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1154,7 +1168,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1173,7 +1187,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1192,7 +1206,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1211,7 +1225,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1230,7 +1244,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1249,7 +1263,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1268,7 +1282,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1287,7 +1301,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1306,7 +1320,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1325,7 +1339,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1344,7 +1358,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1363,7 +1377,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1382,7 +1396,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1401,7 +1415,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1420,7 +1434,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1439,7 +1453,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1458,7 +1472,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1477,7 +1491,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1496,7 +1510,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1515,7 +1529,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -1534,7 +1548,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1553,7 +1567,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1572,7 +1586,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -1591,7 +1605,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1610,7 +1624,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1629,7 +1643,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1648,7 +1662,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1667,7 +1681,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1686,7 +1700,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1705,7 +1719,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1724,7 +1738,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1743,7 +1757,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1762,7 +1776,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1781,7 +1795,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1800,7 +1814,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1819,7 +1833,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1838,7 +1852,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1857,7 +1871,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -1876,7 +1890,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -1895,7 +1909,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -1914,7 +1928,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -1933,7 +1947,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -1952,7 +1966,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -1971,7 +1985,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -1990,7 +2004,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2011,7 +2025,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2032,7 +2046,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -2053,7 +2067,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2074,7 +2088,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2095,7 +2109,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -2116,7 +2130,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2137,7 +2151,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2158,7 +2172,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -2179,7 +2193,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2200,7 +2214,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2221,7 +2235,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -2242,7 +2256,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2263,7 +2277,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2284,7 +2298,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -2305,7 +2319,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2326,7 +2340,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2347,7 +2361,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -2368,7 +2382,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2389,7 +2403,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2410,7 +2424,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2431,7 +2445,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2452,7 +2466,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2473,7 +2487,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -2494,7 +2508,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2517,7 +2531,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2540,7 +2554,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -2563,7 +2577,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2586,7 +2600,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -2609,7 +2623,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -2632,7 +2646,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2655,7 +2669,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2678,7 +2692,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2701,7 +2715,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -2724,7 +2738,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -2747,7 +2761,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -2770,7 +2784,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2793,7 +2807,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -2816,7 +2830,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="n">
@@ -2841,7 +2855,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -2864,7 +2878,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -2887,7 +2901,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="n">
@@ -2912,7 +2926,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -2935,7 +2949,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -2958,7 +2972,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="n">
@@ -2983,7 +2997,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -3006,7 +3020,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -3029,7 +3043,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="n">
@@ -3054,7 +3068,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -3079,7 +3093,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -3104,7 +3118,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -3131,7 +3145,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3156,7 +3170,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3181,7 +3195,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -3208,7 +3222,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3233,7 +3247,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3258,7 +3272,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -3285,7 +3299,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3310,7 +3324,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3335,7 +3349,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -3362,7 +3376,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3387,7 +3401,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3412,7 +3426,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -3439,7 +3453,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3464,7 +3478,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -3489,7 +3503,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -3516,7 +3530,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3541,7 +3555,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3566,7 +3580,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -3593,7 +3607,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -3618,7 +3632,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -3643,7 +3657,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -3670,7 +3684,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -3695,7 +3709,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -3720,7 +3734,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -3747,7 +3761,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -3772,7 +3786,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -3797,7 +3811,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -3824,7 +3838,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -3849,7 +3863,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -3874,7 +3888,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -3901,7 +3915,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -3926,7 +3940,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -3951,7 +3965,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -3978,7 +3992,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -4005,7 +4019,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -4032,7 +4046,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -4061,7 +4075,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -4088,7 +4102,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -4115,7 +4129,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -4144,7 +4158,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -4171,7 +4185,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -4198,7 +4212,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -4227,7 +4241,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4254,7 +4268,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4281,7 +4295,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -4310,7 +4324,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4339,7 +4353,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4368,7 +4382,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -4399,7 +4413,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4428,7 +4442,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4457,7 +4471,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -4488,7 +4502,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -4517,7 +4531,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -4546,7 +4560,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -4577,7 +4591,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -4606,7 +4620,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -4635,7 +4649,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -4666,7 +4680,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -4695,7 +4709,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -4724,7 +4738,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -4755,7 +4769,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -4784,7 +4798,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -4813,7 +4827,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -4844,7 +4858,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -4873,7 +4887,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -4902,7 +4916,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -4933,7 +4947,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -4962,7 +4976,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -4991,7 +5005,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -5022,7 +5036,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -5051,7 +5065,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -5080,7 +5094,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -5111,7 +5125,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -5140,7 +5154,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -5169,7 +5183,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -5200,7 +5214,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -5229,7 +5243,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -5258,7 +5272,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -5289,7 +5303,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -5318,7 +5332,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -5347,7 +5361,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -5378,7 +5392,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -5407,7 +5421,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -5436,7 +5450,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -5467,7 +5481,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -5496,7 +5510,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -5525,7 +5539,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -5556,7 +5570,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -5585,7 +5599,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -5614,7 +5628,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -5645,7 +5659,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -5674,7 +5688,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -5703,7 +5717,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -5734,7 +5748,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -5763,7 +5777,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -5792,7 +5806,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -5823,7 +5837,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -5852,7 +5866,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -5881,7 +5895,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -5912,7 +5926,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -5941,7 +5955,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -5970,7 +5984,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -6001,7 +6015,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -6030,7 +6044,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -6059,7 +6073,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -6090,7 +6104,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -6121,7 +6135,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -6152,7 +6166,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -6185,7 +6199,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -6216,7 +6230,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -6247,7 +6261,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -6280,7 +6294,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -6311,7 +6325,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -6342,7 +6356,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -6375,7 +6389,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -6406,7 +6420,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -6437,7 +6451,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -6470,7 +6484,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -6501,7 +6515,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -6532,7 +6546,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -6565,7 +6579,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -6596,7 +6610,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -6627,7 +6641,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -6660,7 +6674,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -6691,7 +6705,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -6722,7 +6736,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -6755,7 +6769,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -6786,7 +6800,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -6817,7 +6831,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -6850,7 +6864,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -6881,7 +6895,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -6912,7 +6926,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -6945,7 +6959,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -6976,7 +6990,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -7007,7 +7021,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -7040,7 +7054,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -7071,7 +7085,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -7102,7 +7116,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -7135,7 +7149,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -7166,7 +7180,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -7197,7 +7211,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -7230,7 +7244,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -7261,7 +7275,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -7292,7 +7306,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -7325,7 +7339,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -7356,7 +7370,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -7387,7 +7401,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -7420,7 +7434,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -7451,7 +7465,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -7482,7 +7496,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -7515,7 +7529,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -7546,7 +7560,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -7577,7 +7591,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -7610,7 +7624,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -7641,7 +7655,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -7672,7 +7686,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -7705,7 +7719,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -7736,7 +7750,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -7767,7 +7781,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -7800,7 +7814,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -7831,7 +7845,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -7862,7 +7876,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -7895,7 +7909,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -7926,7 +7940,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -7957,7 +7971,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -7990,7 +8004,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -8021,7 +8035,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -8052,7 +8066,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -8085,7 +8099,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -8116,7 +8130,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -8147,7 +8161,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -8180,7 +8194,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -8211,7 +8225,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -8242,7 +8256,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -8275,7 +8289,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -8306,7 +8320,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -8337,7 +8351,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -8370,7 +8384,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -8401,7 +8415,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -8432,7 +8446,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -8465,7 +8479,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -8496,7 +8510,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -8527,7 +8541,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -8560,7 +8574,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -8591,7 +8605,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -8622,7 +8636,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -8655,7 +8669,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -8686,7 +8700,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -8717,7 +8731,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -8750,7 +8764,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -8781,7 +8795,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -8812,7 +8826,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -8845,7 +8859,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -8876,7 +8890,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -8907,7 +8921,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -8940,7 +8954,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -8971,7 +8985,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -9002,7 +9016,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -9035,7 +9049,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -9066,7 +9080,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -9097,7 +9111,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -9130,7 +9144,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -9161,7 +9175,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -9192,7 +9206,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -9225,7 +9239,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -9256,7 +9270,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -9287,7 +9301,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -9320,7 +9334,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -9351,7 +9365,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -9382,7 +9396,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -9415,7 +9429,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -9446,7 +9460,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -9477,7 +9491,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -9510,7 +9524,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -9541,7 +9555,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -9572,7 +9586,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -9605,7 +9619,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -9636,7 +9650,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -9667,7 +9681,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -9700,7 +9714,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -9731,7 +9745,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -9762,7 +9776,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -9795,7 +9809,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -9826,7 +9840,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -9857,7 +9871,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -9890,7 +9904,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -9921,7 +9935,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -9952,7 +9966,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -9985,7 +9999,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -10016,7 +10030,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -10047,7 +10061,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -10080,7 +10094,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -10111,7 +10125,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -10142,7 +10156,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -10175,7 +10189,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -10206,7 +10220,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -10237,7 +10251,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -10270,7 +10284,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -10301,7 +10315,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -10332,7 +10346,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -10365,7 +10379,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -10396,7 +10410,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -10427,7 +10441,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -10460,7 +10474,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -10491,7 +10505,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -10522,7 +10536,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -10555,7 +10569,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -10586,7 +10600,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -10617,7 +10631,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -10650,7 +10664,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -10681,7 +10695,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -10712,7 +10726,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -10745,7 +10759,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -10776,7 +10790,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -10807,7 +10821,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -10840,7 +10854,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -10871,7 +10885,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -10902,7 +10916,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -10935,7 +10949,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -10966,7 +10980,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -10997,7 +11011,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -11030,7 +11044,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -11061,7 +11075,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -11092,7 +11106,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -11125,7 +11139,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -11156,7 +11170,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -11187,7 +11201,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -11220,7 +11234,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -11251,7 +11265,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -11282,7 +11296,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -11315,7 +11329,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -11346,7 +11360,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -11377,7 +11391,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -11410,7 +11424,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -11441,7 +11455,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -11472,7 +11486,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -11505,7 +11519,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -11536,7 +11550,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -11567,7 +11581,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -11600,7 +11614,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -11631,7 +11645,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -11662,7 +11676,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -11695,7 +11709,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -11726,7 +11740,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -11757,7 +11771,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -11790,7 +11804,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -11821,7 +11835,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -11852,7 +11866,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -11885,7 +11899,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -11916,7 +11930,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -11947,7 +11961,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -11980,7 +11994,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -12011,7 +12025,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -12042,7 +12056,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -12075,7 +12089,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -12106,7 +12120,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -12137,7 +12151,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -12170,7 +12184,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -12201,7 +12215,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -12232,7 +12246,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -12265,7 +12279,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -12296,7 +12310,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -12327,7 +12341,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -12360,7 +12374,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -12391,7 +12405,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -12422,7 +12436,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -12455,7 +12469,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -12486,7 +12500,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -12517,7 +12531,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -12550,7 +12564,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -12581,7 +12595,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -12612,7 +12626,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -12645,7 +12659,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -12676,7 +12690,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -12707,7 +12721,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -12740,7 +12754,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -12771,7 +12785,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -12802,7 +12816,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -12835,7 +12849,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -12866,7 +12880,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -12897,7 +12911,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -12930,7 +12944,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -12961,7 +12975,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -12992,7 +13006,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -13025,7 +13039,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -13056,7 +13070,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -13087,7 +13101,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -13120,7 +13134,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -13151,7 +13165,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -13182,7 +13196,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -13215,7 +13229,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -13246,7 +13260,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -13277,7 +13291,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -13310,7 +13324,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -13341,7 +13355,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -13372,7 +13386,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -13405,7 +13419,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -13436,7 +13450,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -13467,7 +13481,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -13500,7 +13514,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -13531,7 +13545,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -13562,7 +13576,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -13595,7 +13609,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -13626,7 +13640,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -13657,7 +13671,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -13690,7 +13704,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -13721,7 +13735,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -13752,7 +13766,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -13785,7 +13799,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -13816,7 +13830,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -13847,7 +13861,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -13880,7 +13894,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -13911,7 +13925,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -13942,7 +13956,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -13975,7 +13989,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -14006,7 +14020,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -14037,7 +14051,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -14070,7 +14084,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -14101,7 +14115,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -14132,7 +14146,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -14165,7 +14179,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -14196,7 +14210,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -14227,7 +14241,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -14260,7 +14274,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -14291,7 +14305,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -14322,7 +14336,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>

--- a/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/ES_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K502"/>
+  <dimension ref="A1:K503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>4.726502471155617</v>
+        <v>4.725616339063959</v>
       </c>
       <c r="H205" t="n">
         <v>10.7</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="n">
-        <v>4.752727750345706</v>
+        <v>4.753590191106364</v>
       </c>
       <c r="H221" t="n">
         <v>11.4</v>
@@ -6216,7 +6216,7 @@
         <v>5.376203905205108</v>
       </c>
       <c r="G245" t="n">
-        <v>4.800736969532067</v>
+        <v>4.801558999993482</v>
       </c>
       <c r="H245" t="n">
         <v>9.699999999999999</v>
@@ -6660,7 +6660,7 @@
         <v>5.424068571853597</v>
       </c>
       <c r="G259" t="n">
-        <v>4.809742351716865</v>
+        <v>4.808927023502111</v>
       </c>
       <c r="H259" t="n">
         <v>8.4</v>
@@ -6746,7 +6746,7 @@
         <v>3.335381</v>
       </c>
       <c r="D262" t="n">
-        <v>4.658710952916121</v>
+        <v>4.659658371272161</v>
       </c>
       <c r="E262" t="n">
         <v>4.859036909945142</v>
@@ -6777,7 +6777,7 @@
         <v>3.502</v>
       </c>
       <c r="D263" t="n">
-        <v>4.661550519424199</v>
+        <v>4.660604892876192</v>
       </c>
       <c r="E263" t="n">
         <v>4.857484114602081</v>
@@ -7325,7 +7325,7 @@
         <v>5.24649761781824</v>
       </c>
       <c r="G280" t="n">
-        <v>4.795790545596741</v>
+        <v>4.794963757620747</v>
       </c>
       <c r="H280" t="n">
         <v>9.5</v>
@@ -7356,7 +7356,7 @@
         <v>5.240158452374504</v>
       </c>
       <c r="G281" t="n">
-        <v>4.804021044733257</v>
+        <v>4.804840381116659</v>
       </c>
       <c r="H281" t="n">
         <v>10</v>
@@ -7546,7 +7546,7 @@
         <v>5.132262782217954</v>
       </c>
       <c r="G287" t="n">
-        <v>4.762173934797756</v>
+        <v>4.763028270603671</v>
       </c>
       <c r="H287" t="n">
         <v>12.9</v>
@@ -7957,7 +7957,7 @@
         <v>5.021904886354487</v>
       </c>
       <c r="G300" t="n">
-        <v>4.715816706075155</v>
+        <v>4.71492104994721</v>
       </c>
       <c r="H300" t="n">
         <v>18.7</v>
@@ -8214,7 +8214,7 @@
         <v>4.690430029938915</v>
       </c>
       <c r="H308" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="I308" t="n">
         <v>4.302171409424417</v>
@@ -8373,7 +8373,7 @@
         <v>4.670957926526095</v>
       </c>
       <c r="H313" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="I313" t="n">
         <v>4.326646051321076</v>
@@ -9256,7 +9256,7 @@
         <v>4.542230386214217</v>
       </c>
       <c r="G341" t="n">
-        <v>4.499809670330265</v>
+        <v>4.498697941477575</v>
       </c>
       <c r="H341" t="n">
         <v>26.3</v>
@@ -9636,10 +9636,10 @@
         <v>4.841032509710076</v>
       </c>
       <c r="G353" t="n">
-        <v>4.506454213048934</v>
+        <v>4.507557357121091</v>
       </c>
       <c r="H353" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="I353" t="n">
         <v>4.384523514872469</v>
@@ -9829,7 +9829,7 @@
         <v>4.515245478460105</v>
       </c>
       <c r="H359" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="I359" t="n">
         <v>4.380024632003209</v>
@@ -10080,7 +10080,7 @@
         <v>4.762173934797756</v>
       </c>
       <c r="G367" t="n">
-        <v>4.537961436294641</v>
+        <v>4.536891345234797</v>
       </c>
       <c r="H367" t="n">
         <v>22.3</v>
@@ -10209,7 +10209,7 @@
         <v>4.56954300834494</v>
       </c>
       <c r="H371" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="I371" t="n">
         <v>4.371092069621102</v>
@@ -10228,7 +10228,7 @@
         <v>-0.087619</v>
       </c>
       <c r="D372" t="n">
-        <v>4.674696248636701</v>
+        <v>4.673762977453703</v>
       </c>
       <c r="E372" t="n">
         <v>4.591071261608589</v>
@@ -10494,7 +10494,7 @@
         <v>4.597138014290827</v>
       </c>
       <c r="H380" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="I380" t="n">
         <v>4.361441201064773</v>
@@ -10577,7 +10577,7 @@
         <v>-0.309</v>
       </c>
       <c r="D383" t="n">
-        <v>4.676560182074764</v>
+        <v>4.675628649636653</v>
       </c>
       <c r="E383" t="n">
         <v>4.584967478670572</v>
@@ -10681,7 +10681,7 @@
         <v>4.814620410170298</v>
       </c>
       <c r="G386" t="n">
-        <v>4.593097604753822</v>
+        <v>4.592084946439436</v>
       </c>
       <c r="H386" t="n">
         <v>18.3</v>
@@ -10779,7 +10779,7 @@
         <v>4.605170185988092</v>
       </c>
       <c r="H389" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="I389" t="n">
         <v>4.390862483336281</v>
@@ -11000,7 +11000,7 @@
         <v>4.611152257665639</v>
       </c>
       <c r="H396" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="I396" t="n">
         <v>4.395929539842873</v>
@@ -11306,7 +11306,7 @@
         <v>-0.31885</v>
       </c>
       <c r="D406" t="n">
-        <v>4.654912277882906</v>
+        <v>4.65586330030361</v>
       </c>
       <c r="E406" t="n">
         <v>4.621043535144381</v>
@@ -11410,7 +11410,7 @@
         <v>4.832305758571839</v>
       </c>
       <c r="G409" t="n">
-        <v>4.616110126026426</v>
+        <v>4.61512051684126</v>
       </c>
       <c r="H409" t="n">
         <v>14.4</v>
@@ -11441,7 +11441,7 @@
         <v>4.817859279398442</v>
       </c>
       <c r="G410" t="n">
-        <v>4.625952725170619</v>
+        <v>4.626931677769604</v>
       </c>
       <c r="H410" t="n">
         <v>14.3</v>
@@ -11622,7 +11622,7 @@
         <v>-0.3648696</v>
       </c>
       <c r="D416" t="n">
-        <v>4.658710952916121</v>
+        <v>4.659658371272161</v>
       </c>
       <c r="E416" t="n">
         <v>4.619073091157083</v>
@@ -11686,7 +11686,7 @@
         <v>-0.4175714</v>
       </c>
       <c r="D418" t="n">
-        <v>4.637637376125593</v>
+        <v>4.638604962074329</v>
       </c>
       <c r="E418" t="n">
         <v>4.625952725170619</v>
@@ -11717,7 +11717,7 @@
         <v>-0.4128696</v>
       </c>
       <c r="D419" t="n">
-        <v>4.614129927359564</v>
+        <v>4.613138355637268</v>
       </c>
       <c r="E419" t="n">
         <v>4.641502115235482</v>
@@ -11726,7 +11726,7 @@
         <v>4.789988622980633</v>
       </c>
       <c r="G419" t="n">
-        <v>4.634728988229636</v>
+        <v>4.635699391022914</v>
       </c>
       <c r="H419" t="n">
         <v>14</v>
@@ -11938,7 +11938,7 @@
         <v>-0.27195</v>
       </c>
       <c r="D426" t="n">
-        <v>4.238444906195857</v>
+        <v>4.239886867512759</v>
       </c>
       <c r="E426" t="n">
         <v>4.352855257373601</v>
@@ -12097,7 +12097,7 @@
         <v>-0.5091364</v>
       </c>
       <c r="D431" t="n">
-        <v>4.506454213048934</v>
+        <v>4.505349850705881</v>
       </c>
       <c r="E431" t="n">
         <v>4.602165676967792</v>
@@ -12287,7 +12287,7 @@
         <v>-0.53815</v>
       </c>
       <c r="D437" t="n">
-        <v>4.629862798578463</v>
+        <v>4.630837932736669</v>
       </c>
       <c r="E437" t="n">
         <v>4.598145571051127</v>
@@ -12446,7 +12446,7 @@
         <v>-0.5450455</v>
       </c>
       <c r="D442" t="n">
-        <v>4.695010889987881</v>
+        <v>4.695924549256556</v>
       </c>
       <c r="E442" t="n">
         <v>4.598145571051127</v>
@@ -12458,7 +12458,7 @@
         <v>4.618086411254637</v>
       </c>
       <c r="H442" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="I442" t="n">
         <v>4.44464925915299</v>
@@ -12541,7 +12541,7 @@
         <v>-0.5819565</v>
       </c>
       <c r="D445" t="n">
-        <v>4.683056724645162</v>
+        <v>4.68213122712422</v>
       </c>
       <c r="E445" t="n">
         <v>4.638604962074329</v>
@@ -12793,7 +12793,7 @@
         <v>0.3947391</v>
       </c>
       <c r="D453" t="n">
-        <v>4.574710978503383</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="E453" t="n">
         <v>4.640537329825382</v>
@@ -13120,7 +13120,7 @@
         <v>4.561218298458908</v>
       </c>
       <c r="G463" t="n">
-        <v>4.654912277882906</v>
+        <v>4.653960350157523</v>
       </c>
       <c r="H463" t="n">
         <v>11.9</v>
@@ -13151,7 +13151,7 @@
         <v>4.554928969551344</v>
       </c>
       <c r="G464" t="n">
-        <v>4.65681341913993</v>
+        <v>4.65586330030361</v>
       </c>
       <c r="H464" t="n">
         <v>12</v>
@@ -13215,7 +13215,7 @@
         <v>4.565389315976247</v>
       </c>
       <c r="G466" t="n">
-        <v>4.642465970731788</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="H466" t="n">
         <v>12</v>
@@ -13237,7 +13237,7 @@
         <v>3.9676364</v>
       </c>
       <c r="D467" t="n">
-        <v>4.60816569496789</v>
+        <v>4.607168188650764</v>
       </c>
       <c r="E467" t="n">
         <v>4.602165676967792</v>
@@ -13372,10 +13372,10 @@
         <v>4.561218298458908</v>
       </c>
       <c r="G471" t="n">
-        <v>4.658710952916121</v>
+        <v>4.657762636107262</v>
       </c>
       <c r="H471" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="I471" t="n">
         <v>4.561949483533528</v>
@@ -13408,7 +13408,7 @@
         <v>4.653960350157523</v>
       </c>
       <c r="H472" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="I472" t="n">
         <v>4.57532934397707</v>
@@ -13436,7 +13436,7 @@
         <v>4.554928969551344</v>
       </c>
       <c r="G473" t="n">
-        <v>4.664382045619937</v>
+        <v>4.663439094112067</v>
       </c>
       <c r="H473" t="n">
         <v>11.6</v>
@@ -13467,7 +13467,7 @@
         <v>4.566429357671661</v>
       </c>
       <c r="G474" t="n">
-        <v>4.658710952916121</v>
+        <v>4.657762636107262</v>
       </c>
       <c r="H474" t="n">
         <v>11.6</v>
@@ -13562,7 +13562,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="G477" t="n">
-        <v>4.673762977453703</v>
+        <v>4.672828834461906</v>
       </c>
       <c r="H477" t="n">
         <v>11.3</v>
@@ -13586,7 +13586,7 @@
         <v>3.4337143</v>
       </c>
       <c r="D478" t="n">
-        <v>4.673762977453703</v>
+        <v>4.674696248636701</v>
       </c>
       <c r="E478" t="n">
         <v>4.616110126026426</v>
@@ -13595,7 +13595,7 @@
         <v>4.598145571051127</v>
       </c>
       <c r="G478" t="n">
-        <v>4.681204872264089</v>
+        <v>4.683056724645162</v>
       </c>
       <c r="H478" t="n">
         <v>11.1</v>
@@ -13617,7 +13617,7 @@
         <v>3.1666087</v>
       </c>
       <c r="D479" t="n">
-        <v>4.611152257665639</v>
+        <v>4.609162207257629</v>
       </c>
       <c r="E479" t="n">
         <v>4.627909672957581</v>
@@ -13648,7 +13648,7 @@
         <v>3.0067619</v>
       </c>
       <c r="D480" t="n">
-        <v>4.629862798578463</v>
+        <v>4.628886712605407</v>
       </c>
       <c r="E480" t="n">
         <v>4.605170185988092</v>
@@ -13816,7 +13816,7 @@
         <v>4.817859279398442</v>
       </c>
       <c r="G485" t="n">
-        <v>4.707726774313183</v>
+        <v>4.706823839714591</v>
       </c>
       <c r="H485" t="n">
         <v>10.6</v>
@@ -13880,10 +13880,10 @@
         <v>4.842611042003125</v>
       </c>
       <c r="G487" t="n">
-        <v>4.716711560720999</v>
+        <v>4.715816706075155</v>
       </c>
       <c r="H487" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="I487" t="n">
         <v>4.610058220060867</v>
@@ -13902,7 +13902,7 @@
         <v>1.9863478</v>
       </c>
       <c r="D488" t="n">
-        <v>4.628886712605407</v>
+        <v>4.629862798578463</v>
       </c>
       <c r="E488" t="n">
         <v>4.625952725170619</v>
@@ -13911,7 +13911,7 @@
         <v>4.821893169499378</v>
       </c>
       <c r="G488" t="n">
-        <v>4.716711560720999</v>
+        <v>4.715816706075155</v>
       </c>
       <c r="H488" t="n">
         <v>10.6</v>
@@ -13933,7 +13933,7 @@
         <v>2.0210952</v>
       </c>
       <c r="D489" t="n">
-        <v>4.619073091157083</v>
+        <v>4.620058798481842</v>
       </c>
       <c r="E489" t="n">
         <v>4.627909672957581</v>
@@ -13942,7 +13942,7 @@
         <v>4.767289035464526</v>
       </c>
       <c r="G489" t="n">
-        <v>4.719391330078114</v>
+        <v>4.718498871295094</v>
       </c>
       <c r="H489" t="n">
         <v>10.5</v>
@@ -13966,7 +13966,7 @@
         <v>2.0272727</v>
       </c>
       <c r="D490" t="n">
-        <v>4.646312129319266</v>
+        <v>4.647271362006727</v>
       </c>
       <c r="E490" t="n">
         <v>4.631812116934513</v>
@@ -13975,7 +13975,7 @@
         <v>4.768988271217486</v>
       </c>
       <c r="G490" t="n">
-        <v>4.721173861744398</v>
+        <v>4.72384171570559</v>
       </c>
       <c r="H490" t="n">
         <v>10.4</v>
@@ -13997,7 +13997,7 @@
         <v>2.0344348</v>
       </c>
       <c r="D491" t="n">
-        <v>4.640537329825382</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="E491" t="n">
         <v>4.638604962074329</v>
@@ -14028,7 +14028,7 @@
         <v>2.04165</v>
       </c>
       <c r="D492" t="n">
-        <v>4.652053771886941</v>
+        <v>4.651099117876491</v>
       </c>
       <c r="E492" t="n">
         <v>4.649187071404866</v>
@@ -14037,7 +14037,7 @@
         <v>4.760463070394127</v>
       </c>
       <c r="G492" t="n">
-        <v>4.730039168033961</v>
+        <v>4.730921391293652</v>
       </c>
       <c r="H492" t="n">
         <v>10.1</v>
@@ -14123,7 +14123,7 @@
         <v>2.0113</v>
       </c>
       <c r="D495" t="n">
-        <v>4.663439094112067</v>
+        <v>4.662495252607361</v>
       </c>
       <c r="E495" t="n">
         <v>4.618086411254637</v>
@@ -14132,7 +14132,7 @@
         <v>4.700480365792417</v>
       </c>
       <c r="G495" t="n">
-        <v>4.718498871295094</v>
+        <v>4.71760561531788</v>
       </c>
       <c r="H495" t="n">
         <v>10.3</v>
@@ -14150,7 +14150,7 @@
         <v>46112</v>
       </c>
       <c r="B496" t="n">
-        <v>12.77836488947364</v>
+        <v>12.77819560596568</v>
       </c>
       <c r="C496" t="n">
         <v>2.1094091</v>
@@ -14165,7 +14165,7 @@
         <v>4.722063937459591</v>
       </c>
       <c r="G496" t="n">
-        <v>4.729156165769083</v>
+        <v>4.728272383122075</v>
       </c>
       <c r="H496" t="n">
         <v>10.3</v>
@@ -14196,7 +14196,7 @@
         <v>4.730039168033961</v>
       </c>
       <c r="G497" t="n">
-        <v>4.713127327493184</v>
+        <v>4.712229258281499</v>
       </c>
       <c r="H497" t="n">
         <v>10.2</v>
@@ -14227,7 +14227,7 @@
         <v>4.695924549256556</v>
       </c>
       <c r="G498" t="n">
-        <v>4.719391330078114</v>
+        <v>4.718498871295094</v>
       </c>
       <c r="H498" t="n">
         <v>10.2</v>
@@ -14245,7 +14245,7 @@
         <v>46203</v>
       </c>
       <c r="B499" t="n">
-        <v>12.78518569201263</v>
+        <v>12.7847737166973</v>
       </c>
       <c r="C499" t="n">
         <v>2.339</v>
@@ -14260,10 +14260,10 @@
         <v>4.690430029938915</v>
       </c>
       <c r="G499" t="n">
-        <v>4.722063937459591</v>
+        <v>4.721173861744398</v>
       </c>
       <c r="H499" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I499" t="n">
         <v>4.64515983420425</v>
@@ -14282,7 +14282,7 @@
         <v>2.4253913</v>
       </c>
       <c r="D500" t="n">
-        <v>4.647271362006727</v>
+        <v>4.648229675448539</v>
       </c>
       <c r="E500" t="n">
         <v>4.650143551630823</v>
@@ -14291,10 +14291,10 @@
         <v>4.687671407499835</v>
       </c>
       <c r="G500" t="n">
-        <v>4.712229258281499</v>
+        <v>4.711330381816482</v>
       </c>
       <c r="H500" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="I500" t="n">
         <v>4.644967655862158</v>
@@ -14313,7 +14313,7 @@
         <v>2.5131429</v>
       </c>
       <c r="D501" t="n">
-        <v>4.625952725170619</v>
+        <v>4.626931677769604</v>
       </c>
       <c r="E501" t="n">
         <v>4.642465970731788</v>
@@ -14322,10 +14322,10 @@
         <v>4.695010889987881</v>
       </c>
       <c r="G501" t="n">
-        <v>4.71492104994721</v>
+        <v>4.713127327493184</v>
       </c>
       <c r="H501" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="I501" t="n">
         <v>4.651481088851342</v>
@@ -14339,17 +14339,23 @@
       <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="B502" t="inlineStr"/>
+      <c r="B502" t="n">
+        <v>12.79109995134469</v>
+      </c>
       <c r="C502" t="n">
         <v>2.6350455</v>
       </c>
       <c r="D502" t="n">
-        <v>4.658710952916121</v>
+        <v>4.659658371272161</v>
       </c>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
+      <c r="G502" t="n">
+        <v>4.709530201312334</v>
+      </c>
+      <c r="H502" t="n">
+        <v>10.3</v>
+      </c>
       <c r="I502" t="n">
         <v>4.657762636107262</v>
       </c>
@@ -14357,6 +14363,23 @@
         <v>4.596689494135473</v>
       </c>
       <c r="K502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="n">
+        <v>4.654912277882906</v>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
